--- a/mw-historic-data.xlsx
+++ b/mw-historic-data.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P198"/>
+  <dimension ref="A1:P197"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10672,62 +10672,6 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="D198" s="23" t="n">
-        <v>6583</v>
-      </c>
-      <c r="E198" s="24" t="n">
-        <v>7041836263</v>
-      </c>
-      <c r="F198" s="24" t="n">
-        <v>1069700</v>
-      </c>
-      <c r="G198" s="25">
-        <f>IFERROR(F198/F186-1,"")</f>
-        <v/>
-      </c>
-      <c r="H198" s="24" t="n">
-        <v>910000</v>
-      </c>
-      <c r="I198" s="23" t="n">
-        <v>17698</v>
-      </c>
-      <c r="J198" s="23" t="n">
-        <v>26927</v>
-      </c>
-      <c r="K198" s="25" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="L198" s="26">
-        <f>J198/D198</f>
-        <v/>
-      </c>
-      <c r="M198" s="26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N198" s="27" t="n">
-        <v>27</v>
-      </c>
-      <c r="O198" s="27" t="n">
-        <v>42</v>
-      </c>
-      <c r="P198" s="25" t="n">
-        <v>0.98</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10741,7 +10685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P198"/>
+  <dimension ref="A1:P197"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -20983,62 +20927,6 @@
         <v>0.979</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="D198" s="23" t="n">
-        <v>1183</v>
-      </c>
-      <c r="E198" s="24" t="n">
-        <v>1392781792</v>
-      </c>
-      <c r="F198" s="24" t="n">
-        <v>1177330</v>
-      </c>
-      <c r="G198" s="25">
-        <f>IFERROR(F198/F186-1,"")</f>
-        <v/>
-      </c>
-      <c r="H198" s="24" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="I198" s="23" t="n">
-        <v>3323</v>
-      </c>
-      <c r="J198" s="23" t="n">
-        <v>5252</v>
-      </c>
-      <c r="K198" s="25" t="n">
-        <v>0.339</v>
-      </c>
-      <c r="L198" s="26">
-        <f>J198/D198</f>
-        <v/>
-      </c>
-      <c r="M198" s="26" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N198" s="27" t="n">
-        <v>28</v>
-      </c>
-      <c r="O198" s="27" t="n">
-        <v>42</v>
-      </c>
-      <c r="P198" s="25" t="n">
-        <v>0.98</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -21052,7 +20940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P198"/>
+  <dimension ref="A1:P197"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -31294,62 +31182,6 @@
         <v>0.988</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="D198" s="23" t="n">
-        <v>2377</v>
-      </c>
-      <c r="E198" s="24" t="n">
-        <v>2634409008</v>
-      </c>
-      <c r="F198" s="24" t="n">
-        <v>1108292</v>
-      </c>
-      <c r="G198" s="25">
-        <f>IFERROR(F198/F186-1,"")</f>
-        <v/>
-      </c>
-      <c r="H198" s="24" t="n">
-        <v>885000</v>
-      </c>
-      <c r="I198" s="23" t="n">
-        <v>6401</v>
-      </c>
-      <c r="J198" s="23" t="n">
-        <v>9916</v>
-      </c>
-      <c r="K198" s="25" t="n">
-        <v>0.366</v>
-      </c>
-      <c r="L198" s="26">
-        <f>J198/D198</f>
-        <v/>
-      </c>
-      <c r="M198" s="26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N198" s="27" t="n">
-        <v>26</v>
-      </c>
-      <c r="O198" s="27" t="n">
-        <v>40</v>
-      </c>
-      <c r="P198" s="25" t="n">
-        <v>0.99</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -31363,7 +31195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P198"/>
+  <dimension ref="A1:P197"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -41605,62 +41437,6 @@
         <v>0.969</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="D198" s="23" t="n">
-        <v>247</v>
-      </c>
-      <c r="E198" s="24" t="n">
-        <v>216306128</v>
-      </c>
-      <c r="F198" s="24" t="n">
-        <v>875733</v>
-      </c>
-      <c r="G198" s="25">
-        <f>IFERROR(F198/F186-1,"")</f>
-        <v/>
-      </c>
-      <c r="H198" s="24" t="n">
-        <v>815000</v>
-      </c>
-      <c r="I198" s="23" t="n">
-        <v>657</v>
-      </c>
-      <c r="J198" s="23" t="n">
-        <v>1122</v>
-      </c>
-      <c r="K198" s="25" t="n">
-        <v>0.307</v>
-      </c>
-      <c r="L198" s="26">
-        <f>J198/D198</f>
-        <v/>
-      </c>
-      <c r="M198" s="26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="N198" s="27" t="n">
-        <v>34</v>
-      </c>
-      <c r="O198" s="27" t="n">
-        <v>49</v>
-      </c>
-      <c r="P198" s="25" t="n">
-        <v>0.96</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -41674,7 +41450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P198"/>
+  <dimension ref="A1:P197"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -51916,62 +51692,6 @@
         <v>0.973</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="D198" s="23" t="n">
-        <v>1106</v>
-      </c>
-      <c r="E198" s="24" t="n">
-        <v>1057356568</v>
-      </c>
-      <c r="F198" s="24" t="n">
-        <v>956019</v>
-      </c>
-      <c r="G198" s="25">
-        <f>IFERROR(F198/F186-1,"")</f>
-        <v/>
-      </c>
-      <c r="H198" s="24" t="n">
-        <v>875000</v>
-      </c>
-      <c r="I198" s="23" t="n">
-        <v>3267</v>
-      </c>
-      <c r="J198" s="23" t="n">
-        <v>5053</v>
-      </c>
-      <c r="K198" s="25" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="L198" s="26">
-        <f>J198/D198</f>
-        <v/>
-      </c>
-      <c r="M198" s="26" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N198" s="27" t="n">
-        <v>29</v>
-      </c>
-      <c r="O198" s="27" t="n">
-        <v>44</v>
-      </c>
-      <c r="P198" s="25" t="n">
-        <v>0.98</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -51985,7 +51705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P198"/>
+  <dimension ref="A1:P197"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -62227,62 +61947,6 @@
         <v>0.961</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="D198" s="23" t="n">
-        <v>816</v>
-      </c>
-      <c r="E198" s="24" t="n">
-        <v>1018593994</v>
-      </c>
-      <c r="F198" s="24" t="n">
-        <v>1248277</v>
-      </c>
-      <c r="G198" s="25">
-        <f>IFERROR(F198/F186-1,"")</f>
-        <v/>
-      </c>
-      <c r="H198" s="24" t="n">
-        <v>1050000</v>
-      </c>
-      <c r="I198" s="23" t="n">
-        <v>1969</v>
-      </c>
-      <c r="J198" s="23" t="n">
-        <v>2870</v>
-      </c>
-      <c r="K198" s="25" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="L198" s="26">
-        <f>J198/D198</f>
-        <v/>
-      </c>
-      <c r="M198" s="26" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N198" s="27" t="n">
-        <v>29</v>
-      </c>
-      <c r="O198" s="27" t="n">
-        <v>44</v>
-      </c>
-      <c r="P198" s="25" t="n">
-        <v>0.97</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -62296,7 +61960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P198"/>
+  <dimension ref="A1:P197"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -72538,62 +72202,6 @@
         <v>0.993</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="D198" s="23" t="n">
-        <v>804</v>
-      </c>
-      <c r="E198" s="24" t="n">
-        <v>684255873</v>
-      </c>
-      <c r="F198" s="24" t="n">
-        <v>851065</v>
-      </c>
-      <c r="G198" s="25">
-        <f>IFERROR(F198/F186-1,"")</f>
-        <v/>
-      </c>
-      <c r="H198" s="24" t="n">
-        <v>801000</v>
-      </c>
-      <c r="I198" s="23" t="n">
-        <v>1978</v>
-      </c>
-      <c r="J198" s="23" t="n">
-        <v>2563</v>
-      </c>
-      <c r="K198" s="25" t="n">
-        <v>0.404</v>
-      </c>
-      <c r="L198" s="26">
-        <f>J198/D198</f>
-        <v/>
-      </c>
-      <c r="M198" s="26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N198" s="27" t="n">
-        <v>24</v>
-      </c>
-      <c r="O198" s="27" t="n">
-        <v>37</v>
-      </c>
-      <c r="P198" s="25" t="n">
-        <v>0.99</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -72607,7 +72215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P198"/>
+  <dimension ref="A1:P197"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -82849,62 +82457,6 @@
         <v>0.971</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="D198" s="23" t="n">
-        <v>50</v>
-      </c>
-      <c r="E198" s="24" t="n">
-        <v>38132900</v>
-      </c>
-      <c r="F198" s="24" t="n">
-        <v>762658</v>
-      </c>
-      <c r="G198" s="25">
-        <f>IFERROR(F198/F186-1,"")</f>
-        <v/>
-      </c>
-      <c r="H198" s="24" t="n">
-        <v>733000</v>
-      </c>
-      <c r="I198" s="23" t="n">
-        <v>103</v>
-      </c>
-      <c r="J198" s="23" t="n">
-        <v>151</v>
-      </c>
-      <c r="K198" s="25" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="L198" s="26">
-        <f>J198/D198</f>
-        <v/>
-      </c>
-      <c r="M198" s="26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N198" s="27" t="n">
-        <v>33</v>
-      </c>
-      <c r="O198" s="27" t="n">
-        <v>41</v>
-      </c>
-      <c r="P198" s="25" t="n">
-        <v>0.97</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/mw-historic-data.xlsx
+++ b/mw-historic-data.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="780" windowWidth="26360" windowHeight="20380" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRREB" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="York Region" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Toronto" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simcoe" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peel" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Halton" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Durham" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dufferin" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="TRREB" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="York Region" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Toronto" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Simcoe" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Peel" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Halton" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Durham" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Dufferin" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TRREB'!$A$1:$P$1</definedName>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P197"/>
+  <dimension ref="A1:P198"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10672,6 +10672,62 @@
         <v>0.98</v>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="D198" s="23" t="n">
+        <v>6583</v>
+      </c>
+      <c r="E198" s="24" t="n">
+        <v>7041836263</v>
+      </c>
+      <c r="F198" s="24" t="n">
+        <v>1069700</v>
+      </c>
+      <c r="G198" s="25">
+        <f>IFERROR(F198/F186-1,"")</f>
+        <v/>
+      </c>
+      <c r="H198" s="24" t="n">
+        <v>910000</v>
+      </c>
+      <c r="I198" s="23" t="n">
+        <v>17698</v>
+      </c>
+      <c r="J198" s="23" t="n">
+        <v>26927</v>
+      </c>
+      <c r="K198" s="25" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="L198" s="26">
+        <f>J198/D198</f>
+        <v/>
+      </c>
+      <c r="M198" s="26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N198" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="O198" s="27" t="n">
+        <v>42</v>
+      </c>
+      <c r="P198" s="25" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10685,7 +10741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P197"/>
+  <dimension ref="A1:P198"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -20927,6 +20983,62 @@
         <v>0.979</v>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="D198" s="23" t="n">
+        <v>1183</v>
+      </c>
+      <c r="E198" s="24" t="n">
+        <v>1392781792</v>
+      </c>
+      <c r="F198" s="24" t="n">
+        <v>1177330</v>
+      </c>
+      <c r="G198" s="25">
+        <f>IFERROR(F198/F186-1,"")</f>
+        <v/>
+      </c>
+      <c r="H198" s="24" t="n">
+        <v>1090000</v>
+      </c>
+      <c r="I198" s="23" t="n">
+        <v>3323</v>
+      </c>
+      <c r="J198" s="23" t="n">
+        <v>5252</v>
+      </c>
+      <c r="K198" s="25" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="L198" s="26">
+        <f>J198/D198</f>
+        <v/>
+      </c>
+      <c r="M198" s="26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N198" s="27" t="n">
+        <v>28</v>
+      </c>
+      <c r="O198" s="27" t="n">
+        <v>42</v>
+      </c>
+      <c r="P198" s="25" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -20940,7 +21052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P197"/>
+  <dimension ref="A1:P198"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -31182,6 +31294,62 @@
         <v>0.988</v>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="D198" s="23" t="n">
+        <v>2377</v>
+      </c>
+      <c r="E198" s="24" t="n">
+        <v>2634409008</v>
+      </c>
+      <c r="F198" s="24" t="n">
+        <v>1108292</v>
+      </c>
+      <c r="G198" s="25">
+        <f>IFERROR(F198/F186-1,"")</f>
+        <v/>
+      </c>
+      <c r="H198" s="24" t="n">
+        <v>885000</v>
+      </c>
+      <c r="I198" s="23" t="n">
+        <v>6401</v>
+      </c>
+      <c r="J198" s="23" t="n">
+        <v>9916</v>
+      </c>
+      <c r="K198" s="25" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="L198" s="26">
+        <f>J198/D198</f>
+        <v/>
+      </c>
+      <c r="M198" s="26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N198" s="27" t="n">
+        <v>26</v>
+      </c>
+      <c r="O198" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="P198" s="25" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -31195,7 +31363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P197"/>
+  <dimension ref="A1:P198"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -41437,6 +41605,62 @@
         <v>0.969</v>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="D198" s="23" t="n">
+        <v>247</v>
+      </c>
+      <c r="E198" s="24" t="n">
+        <v>216306128</v>
+      </c>
+      <c r="F198" s="24" t="n">
+        <v>875733</v>
+      </c>
+      <c r="G198" s="25">
+        <f>IFERROR(F198/F186-1,"")</f>
+        <v/>
+      </c>
+      <c r="H198" s="24" t="n">
+        <v>815000</v>
+      </c>
+      <c r="I198" s="23" t="n">
+        <v>657</v>
+      </c>
+      <c r="J198" s="23" t="n">
+        <v>1122</v>
+      </c>
+      <c r="K198" s="25" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="L198" s="26">
+        <f>J198/D198</f>
+        <v/>
+      </c>
+      <c r="M198" s="26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="N198" s="27" t="n">
+        <v>34</v>
+      </c>
+      <c r="O198" s="27" t="n">
+        <v>49</v>
+      </c>
+      <c r="P198" s="25" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -41450,7 +41674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P197"/>
+  <dimension ref="A1:P198"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -51692,6 +51916,62 @@
         <v>0.973</v>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="D198" s="23" t="n">
+        <v>1106</v>
+      </c>
+      <c r="E198" s="24" t="n">
+        <v>1057356568</v>
+      </c>
+      <c r="F198" s="24" t="n">
+        <v>956019</v>
+      </c>
+      <c r="G198" s="25">
+        <f>IFERROR(F198/F186-1,"")</f>
+        <v/>
+      </c>
+      <c r="H198" s="24" t="n">
+        <v>875000</v>
+      </c>
+      <c r="I198" s="23" t="n">
+        <v>3267</v>
+      </c>
+      <c r="J198" s="23" t="n">
+        <v>5053</v>
+      </c>
+      <c r="K198" s="25" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="L198" s="26">
+        <f>J198/D198</f>
+        <v/>
+      </c>
+      <c r="M198" s="26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N198" s="27" t="n">
+        <v>29</v>
+      </c>
+      <c r="O198" s="27" t="n">
+        <v>44</v>
+      </c>
+      <c r="P198" s="25" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -51705,7 +51985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P197"/>
+  <dimension ref="A1:P198"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -61947,6 +62227,62 @@
         <v>0.961</v>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="D198" s="23" t="n">
+        <v>816</v>
+      </c>
+      <c r="E198" s="24" t="n">
+        <v>1018593994</v>
+      </c>
+      <c r="F198" s="24" t="n">
+        <v>1248277</v>
+      </c>
+      <c r="G198" s="25">
+        <f>IFERROR(F198/F186-1,"")</f>
+        <v/>
+      </c>
+      <c r="H198" s="24" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="I198" s="23" t="n">
+        <v>1969</v>
+      </c>
+      <c r="J198" s="23" t="n">
+        <v>2870</v>
+      </c>
+      <c r="K198" s="25" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="L198" s="26">
+        <f>J198/D198</f>
+        <v/>
+      </c>
+      <c r="M198" s="26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N198" s="27" t="n">
+        <v>29</v>
+      </c>
+      <c r="O198" s="27" t="n">
+        <v>44</v>
+      </c>
+      <c r="P198" s="25" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -61960,7 +62296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P197"/>
+  <dimension ref="A1:P198"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -72202,6 +72538,62 @@
         <v>0.993</v>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="D198" s="23" t="n">
+        <v>804</v>
+      </c>
+      <c r="E198" s="24" t="n">
+        <v>684255873</v>
+      </c>
+      <c r="F198" s="24" t="n">
+        <v>851065</v>
+      </c>
+      <c r="G198" s="25">
+        <f>IFERROR(F198/F186-1,"")</f>
+        <v/>
+      </c>
+      <c r="H198" s="24" t="n">
+        <v>801000</v>
+      </c>
+      <c r="I198" s="23" t="n">
+        <v>1978</v>
+      </c>
+      <c r="J198" s="23" t="n">
+        <v>2563</v>
+      </c>
+      <c r="K198" s="25" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="L198" s="26">
+        <f>J198/D198</f>
+        <v/>
+      </c>
+      <c r="M198" s="26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N198" s="27" t="n">
+        <v>24</v>
+      </c>
+      <c r="O198" s="27" t="n">
+        <v>37</v>
+      </c>
+      <c r="P198" s="25" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -72215,7 +72607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P197"/>
+  <dimension ref="A1:P198"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -82457,6 +82849,62 @@
         <v>0.971</v>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="D198" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="E198" s="24" t="n">
+        <v>38132900</v>
+      </c>
+      <c r="F198" s="24" t="n">
+        <v>762658</v>
+      </c>
+      <c r="G198" s="25">
+        <f>IFERROR(F198/F186-1,"")</f>
+        <v/>
+      </c>
+      <c r="H198" s="24" t="n">
+        <v>733000</v>
+      </c>
+      <c r="I198" s="23" t="n">
+        <v>103</v>
+      </c>
+      <c r="J198" s="23" t="n">
+        <v>151</v>
+      </c>
+      <c r="K198" s="25" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L198" s="26">
+        <f>J198/D198</f>
+        <v/>
+      </c>
+      <c r="M198" s="26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N198" s="27" t="n">
+        <v>33</v>
+      </c>
+      <c r="O198" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="P198" s="25" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/mw-historic-data.xlsx
+++ b/mw-historic-data.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P198"/>
+  <dimension ref="A1:P199"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10728,6 +10728,62 @@
         <v>0.98</v>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="D199" s="23" t="n">
+        <v>6770</v>
+      </c>
+      <c r="E199" s="24" t="n">
+        <v>7167112613</v>
+      </c>
+      <c r="F199" s="24" t="n">
+        <v>1058658</v>
+      </c>
+      <c r="G199" s="25">
+        <f>IFERROR(F199/F187-1,"")</f>
+        <v/>
+      </c>
+      <c r="H199" s="24" t="n">
+        <v>890000</v>
+      </c>
+      <c r="I199" s="23" t="n">
+        <v>17282</v>
+      </c>
+      <c r="J199" s="23" t="n">
+        <v>27329</v>
+      </c>
+      <c r="K199" s="25" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="L199" s="26">
+        <f>J199/D199</f>
+        <v/>
+      </c>
+      <c r="M199" s="26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N199" s="27" t="n">
+        <v>29</v>
+      </c>
+      <c r="O199" s="27" t="n">
+        <v>42</v>
+      </c>
+      <c r="P199" s="25" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10741,7 +10797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P198"/>
+  <dimension ref="A1:P199"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -21039,6 +21095,62 @@
         <v>0.98</v>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="D199" s="23" t="n">
+        <v>1289</v>
+      </c>
+      <c r="E199" s="24" t="n">
+        <v>1508075562</v>
+      </c>
+      <c r="F199" s="24" t="n">
+        <v>1169958</v>
+      </c>
+      <c r="G199" s="25">
+        <f>IFERROR(F199/F187-1,"")</f>
+        <v/>
+      </c>
+      <c r="H199" s="24" t="n">
+        <v>1050888</v>
+      </c>
+      <c r="I199" s="23" t="n">
+        <v>3293</v>
+      </c>
+      <c r="J199" s="23" t="n">
+        <v>5302</v>
+      </c>
+      <c r="K199" s="25" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="L199" s="26">
+        <f>J199/D199</f>
+        <v/>
+      </c>
+      <c r="M199" s="26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N199" s="27" t="n">
+        <v>29</v>
+      </c>
+      <c r="O199" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="P199" s="25" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -21052,7 +21164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P198"/>
+  <dimension ref="A1:P199"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -31350,6 +31462,62 @@
         <v>0.99</v>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="D199" s="23" t="n">
+        <v>2443</v>
+      </c>
+      <c r="E199" s="24" t="n">
+        <v>2641799582</v>
+      </c>
+      <c r="F199" s="24" t="n">
+        <v>1081375</v>
+      </c>
+      <c r="G199" s="25">
+        <f>IFERROR(F199/F187-1,"")</f>
+        <v/>
+      </c>
+      <c r="H199" s="24" t="n">
+        <v>835000</v>
+      </c>
+      <c r="I199" s="23" t="n">
+        <v>6096</v>
+      </c>
+      <c r="J199" s="23" t="n">
+        <v>10047</v>
+      </c>
+      <c r="K199" s="25" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="L199" s="26">
+        <f>J199/D199</f>
+        <v/>
+      </c>
+      <c r="M199" s="26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N199" s="27" t="n">
+        <v>29</v>
+      </c>
+      <c r="O199" s="27" t="n">
+        <v>38</v>
+      </c>
+      <c r="P199" s="25" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -31363,7 +31531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P198"/>
+  <dimension ref="A1:P199"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -41661,6 +41829,62 @@
         <v>0.96</v>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="D199" s="23" t="n">
+        <v>204</v>
+      </c>
+      <c r="E199" s="24" t="n">
+        <v>177308480</v>
+      </c>
+      <c r="F199" s="24" t="n">
+        <v>869159</v>
+      </c>
+      <c r="G199" s="25">
+        <f>IFERROR(F199/F187-1,"")</f>
+        <v/>
+      </c>
+      <c r="H199" s="24" t="n">
+        <v>816000</v>
+      </c>
+      <c r="I199" s="23" t="n">
+        <v>645</v>
+      </c>
+      <c r="J199" s="23" t="n">
+        <v>1166</v>
+      </c>
+      <c r="K199" s="25" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="L199" s="26">
+        <f>J199/D199</f>
+        <v/>
+      </c>
+      <c r="M199" s="26" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="N199" s="27" t="n">
+        <v>37</v>
+      </c>
+      <c r="O199" s="27" t="n">
+        <v>55</v>
+      </c>
+      <c r="P199" s="25" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -41674,7 +41898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P198"/>
+  <dimension ref="A1:P199"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -51972,6 +52196,62 @@
         <v>0.98</v>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="D199" s="23" t="n">
+        <v>1167</v>
+      </c>
+      <c r="E199" s="24" t="n">
+        <v>1127350424</v>
+      </c>
+      <c r="F199" s="24" t="n">
+        <v>966024</v>
+      </c>
+      <c r="G199" s="25">
+        <f>IFERROR(F199/F187-1,"")</f>
+        <v/>
+      </c>
+      <c r="H199" s="24" t="n">
+        <v>875000</v>
+      </c>
+      <c r="I199" s="23" t="n">
+        <v>3267</v>
+      </c>
+      <c r="J199" s="23" t="n">
+        <v>5189</v>
+      </c>
+      <c r="K199" s="25" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="L199" s="26">
+        <f>J199/D199</f>
+        <v/>
+      </c>
+      <c r="M199" s="26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N199" s="27" t="n">
+        <v>29</v>
+      </c>
+      <c r="O199" s="27" t="n">
+        <v>48</v>
+      </c>
+      <c r="P199" s="25" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -51985,7 +52265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P198"/>
+  <dimension ref="A1:P199"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -62283,6 +62563,62 @@
         <v>0.97</v>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="D199" s="23" t="n">
+        <v>785</v>
+      </c>
+      <c r="E199" s="24" t="n">
+        <v>959974786</v>
+      </c>
+      <c r="F199" s="24" t="n">
+        <v>1222898</v>
+      </c>
+      <c r="G199" s="25">
+        <f>IFERROR(F199/F187-1,"")</f>
+        <v/>
+      </c>
+      <c r="H199" s="24" t="n">
+        <v>1060000</v>
+      </c>
+      <c r="I199" s="23" t="n">
+        <v>1846</v>
+      </c>
+      <c r="J199" s="23" t="n">
+        <v>2827</v>
+      </c>
+      <c r="K199" s="25" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="L199" s="26">
+        <f>J199/D199</f>
+        <v/>
+      </c>
+      <c r="M199" s="26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N199" s="27" t="n">
+        <v>28</v>
+      </c>
+      <c r="O199" s="27" t="n">
+        <v>41</v>
+      </c>
+      <c r="P199" s="25" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -62296,7 +62632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P198"/>
+  <dimension ref="A1:P199"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -72594,6 +72930,62 @@
         <v>0.99</v>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="D199" s="23" t="n">
+        <v>849</v>
+      </c>
+      <c r="E199" s="24" t="n">
+        <v>726888680</v>
+      </c>
+      <c r="F199" s="24" t="n">
+        <v>856170</v>
+      </c>
+      <c r="G199" s="25">
+        <f>IFERROR(F199/F187-1,"")</f>
+        <v/>
+      </c>
+      <c r="H199" s="24" t="n">
+        <v>805000</v>
+      </c>
+      <c r="I199" s="23" t="n">
+        <v>2049</v>
+      </c>
+      <c r="J199" s="23" t="n">
+        <v>2637</v>
+      </c>
+      <c r="K199" s="25" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L199" s="26">
+        <f>J199/D199</f>
+        <v/>
+      </c>
+      <c r="M199" s="26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N199" s="27" t="n">
+        <v>24</v>
+      </c>
+      <c r="O199" s="27" t="n">
+        <v>36</v>
+      </c>
+      <c r="P199" s="25" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -72607,7 +72999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P198"/>
+  <dimension ref="A1:P199"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -82905,6 +83297,62 @@
         <v>0.97</v>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="D199" s="23" t="n">
+        <v>33</v>
+      </c>
+      <c r="E199" s="24" t="n">
+        <v>25715099</v>
+      </c>
+      <c r="F199" s="24" t="n">
+        <v>779245</v>
+      </c>
+      <c r="G199" s="25">
+        <f>IFERROR(F199/F187-1,"")</f>
+        <v/>
+      </c>
+      <c r="H199" s="24" t="n">
+        <v>734000</v>
+      </c>
+      <c r="I199" s="23" t="n">
+        <v>86</v>
+      </c>
+      <c r="J199" s="23" t="n">
+        <v>161</v>
+      </c>
+      <c r="K199" s="25" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="L199" s="26">
+        <f>J199/D199</f>
+        <v/>
+      </c>
+      <c r="M199" s="26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N199" s="27" t="n">
+        <v>47</v>
+      </c>
+      <c r="O199" s="27" t="n">
+        <v>68</v>
+      </c>
+      <c r="P199" s="25" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/mw-historic-data.xlsx
+++ b/mw-historic-data.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P199"/>
+  <dimension ref="A1:P200"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10784,6 +10784,62 @@
         <v>0.98</v>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+      <c r="D200" s="23" t="n">
+        <v>5995</v>
+      </c>
+      <c r="E200" s="24" t="n">
+        <v>6018714179</v>
+      </c>
+      <c r="F200" s="24" t="n">
+        <v>1003956</v>
+      </c>
+      <c r="G200" s="25">
+        <f>IFERROR(F200/F188-1,"")</f>
+        <v/>
+      </c>
+      <c r="H200" s="24" t="n">
+        <v>860000</v>
+      </c>
+      <c r="I200" s="23" t="n">
+        <v>14484</v>
+      </c>
+      <c r="J200" s="23" t="n">
+        <v>26098</v>
+      </c>
+      <c r="K200" s="25" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="L200" s="26">
+        <f>J200/D200</f>
+        <v/>
+      </c>
+      <c r="M200" s="26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N200" s="27" t="n">
+        <v>32</v>
+      </c>
+      <c r="O200" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="P200" s="25" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10797,7 +10853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P199"/>
+  <dimension ref="A1:P200"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -21151,6 +21207,62 @@
         <v>0.98</v>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+      <c r="D200" s="23" t="n">
+        <v>1063</v>
+      </c>
+      <c r="E200" s="24" t="n">
+        <v>1218524690</v>
+      </c>
+      <c r="F200" s="24" t="n">
+        <v>1146307</v>
+      </c>
+      <c r="G200" s="25">
+        <f>IFERROR(F200/F188-1,"")</f>
+        <v/>
+      </c>
+      <c r="H200" s="24" t="n">
+        <v>1060000</v>
+      </c>
+      <c r="I200" s="23" t="n">
+        <v>2764</v>
+      </c>
+      <c r="J200" s="23" t="n">
+        <v>5179</v>
+      </c>
+      <c r="K200" s="25" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="L200" s="26">
+        <f>J200/D200</f>
+        <v/>
+      </c>
+      <c r="M200" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="N200" s="27" t="n">
+        <v>34</v>
+      </c>
+      <c r="O200" s="27" t="n">
+        <v>52</v>
+      </c>
+      <c r="P200" s="25" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -21164,7 +21276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P199"/>
+  <dimension ref="A1:P200"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -31518,6 +31630,62 @@
         <v>0.99</v>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+      <c r="D200" s="23" t="n">
+        <v>2242</v>
+      </c>
+      <c r="E200" s="24" t="n">
+        <v>2266294399</v>
+      </c>
+      <c r="F200" s="24" t="n">
+        <v>1010836</v>
+      </c>
+      <c r="G200" s="25">
+        <f>IFERROR(F200/F188-1,"")</f>
+        <v/>
+      </c>
+      <c r="H200" s="24" t="n">
+        <v>800000</v>
+      </c>
+      <c r="I200" s="23" t="n">
+        <v>4980</v>
+      </c>
+      <c r="J200" s="23" t="n">
+        <v>9310</v>
+      </c>
+      <c r="K200" s="25" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="L200" s="26">
+        <f>J200/D200</f>
+        <v/>
+      </c>
+      <c r="M200" s="26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N200" s="27" t="n">
+        <v>32</v>
+      </c>
+      <c r="O200" s="27" t="n">
+        <v>37</v>
+      </c>
+      <c r="P200" s="25" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -31531,7 +31699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P199"/>
+  <dimension ref="A1:P200"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -41885,6 +42053,62 @@
         <v>0.97</v>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+      <c r="D200" s="23" t="n">
+        <v>194</v>
+      </c>
+      <c r="E200" s="24" t="n">
+        <v>159307670</v>
+      </c>
+      <c r="F200" s="24" t="n">
+        <v>821174</v>
+      </c>
+      <c r="G200" s="25">
+        <f>IFERROR(F200/F188-1,"")</f>
+        <v/>
+      </c>
+      <c r="H200" s="24" t="n">
+        <v>780750</v>
+      </c>
+      <c r="I200" s="23" t="n">
+        <v>554</v>
+      </c>
+      <c r="J200" s="23" t="n">
+        <v>1159</v>
+      </c>
+      <c r="K200" s="25" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="L200" s="26">
+        <f>J200/D200</f>
+        <v/>
+      </c>
+      <c r="M200" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="N200" s="27" t="n">
+        <v>39</v>
+      </c>
+      <c r="O200" s="27" t="n">
+        <v>58</v>
+      </c>
+      <c r="P200" s="25" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -41898,7 +42122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P199"/>
+  <dimension ref="A1:P200"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -52252,6 +52476,62 @@
         <v>0.98</v>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+      <c r="D200" s="23" t="n">
+        <v>1053</v>
+      </c>
+      <c r="E200" s="24" t="n">
+        <v>958237222</v>
+      </c>
+      <c r="F200" s="24" t="n">
+        <v>910007</v>
+      </c>
+      <c r="G200" s="25">
+        <f>IFERROR(F200/F188-1,"")</f>
+        <v/>
+      </c>
+      <c r="H200" s="24" t="n">
+        <v>851000</v>
+      </c>
+      <c r="I200" s="23" t="n">
+        <v>2875</v>
+      </c>
+      <c r="J200" s="23" t="n">
+        <v>5055</v>
+      </c>
+      <c r="K200" s="25" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="L200" s="26">
+        <f>J200/D200</f>
+        <v/>
+      </c>
+      <c r="M200" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="N200" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="O200" s="27" t="n">
+        <v>48</v>
+      </c>
+      <c r="P200" s="25" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -52265,7 +52545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P199"/>
+  <dimension ref="A1:P200"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -62619,6 +62899,62 @@
         <v>0.97</v>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+      <c r="D200" s="23" t="n">
+        <v>682</v>
+      </c>
+      <c r="E200" s="24" t="n">
+        <v>785387700</v>
+      </c>
+      <c r="F200" s="24" t="n">
+        <v>1151595</v>
+      </c>
+      <c r="G200" s="25">
+        <f>IFERROR(F200/F188-1,"")</f>
+        <v/>
+      </c>
+      <c r="H200" s="24" t="n">
+        <v>970000</v>
+      </c>
+      <c r="I200" s="23" t="n">
+        <v>1503</v>
+      </c>
+      <c r="J200" s="23" t="n">
+        <v>2659</v>
+      </c>
+      <c r="K200" s="25" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="L200" s="26">
+        <f>J200/D200</f>
+        <v/>
+      </c>
+      <c r="M200" s="26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N200" s="27" t="n">
+        <v>36</v>
+      </c>
+      <c r="O200" s="27" t="n">
+        <v>52</v>
+      </c>
+      <c r="P200" s="25" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -62632,7 +62968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P199"/>
+  <dimension ref="A1:P200"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -72986,6 +73322,62 @@
         <v>0.99</v>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+      <c r="D200" s="23" t="n">
+        <v>725</v>
+      </c>
+      <c r="E200" s="24" t="n">
+        <v>604876398</v>
+      </c>
+      <c r="F200" s="24" t="n">
+        <v>834312</v>
+      </c>
+      <c r="G200" s="25">
+        <f>IFERROR(F200/F188-1,"")</f>
+        <v/>
+      </c>
+      <c r="H200" s="24" t="n">
+        <v>795000</v>
+      </c>
+      <c r="I200" s="23" t="n">
+        <v>1719</v>
+      </c>
+      <c r="J200" s="23" t="n">
+        <v>2579</v>
+      </c>
+      <c r="K200" s="25" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="L200" s="26">
+        <f>J200/D200</f>
+        <v/>
+      </c>
+      <c r="M200" s="26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N200" s="27" t="n">
+        <v>27</v>
+      </c>
+      <c r="O200" s="27" t="n">
+        <v>43</v>
+      </c>
+      <c r="P200" s="25" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -72999,7 +73391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P199"/>
+  <dimension ref="A1:P200"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -83353,6 +83745,62 @@
         <v>0.97</v>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+      <c r="D200" s="23" t="n">
+        <v>36</v>
+      </c>
+      <c r="E200" s="24" t="n">
+        <v>26086100</v>
+      </c>
+      <c r="F200" s="24" t="n">
+        <v>724614</v>
+      </c>
+      <c r="G200" s="25">
+        <f>IFERROR(F200/F188-1,"")</f>
+        <v/>
+      </c>
+      <c r="H200" s="24" t="n">
+        <v>712500</v>
+      </c>
+      <c r="I200" s="23" t="n">
+        <v>89</v>
+      </c>
+      <c r="J200" s="23" t="n">
+        <v>157</v>
+      </c>
+      <c r="K200" s="25" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="L200" s="26">
+        <f>J200/D200</f>
+        <v/>
+      </c>
+      <c r="M200" s="26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N200" s="27" t="n">
+        <v>33</v>
+      </c>
+      <c r="O200" s="27" t="n">
+        <v>47</v>
+      </c>
+      <c r="P200" s="25" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/mw-historic-data.xlsx
+++ b/mw-historic-data.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P200"/>
+  <dimension ref="A1:P201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10840,6 +10840,62 @@
         <v>0.97</v>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+      <c r="D201" s="23" t="n">
+        <v>5057</v>
+      </c>
+      <c r="E201" s="24" t="n">
+        <v>5023675157</v>
+      </c>
+      <c r="F201" s="24" t="n">
+        <v>993410</v>
+      </c>
+      <c r="G201" s="25">
+        <f>IFERROR(F201/F189-1,"")</f>
+        <v/>
+      </c>
+      <c r="H201" s="24" t="n">
+        <v>850000</v>
+      </c>
+      <c r="I201" s="23" t="n">
+        <v>12075</v>
+      </c>
+      <c r="J201" s="23" t="n">
+        <v>24482</v>
+      </c>
+      <c r="K201" s="25" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="L201" s="26">
+        <f>J201/D201</f>
+        <v/>
+      </c>
+      <c r="M201" s="26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N201" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="O201" s="27" t="n">
+        <v>51</v>
+      </c>
+      <c r="P201" s="25" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10853,7 +10909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P200"/>
+  <dimension ref="A1:P201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -21263,6 +21319,62 @@
         <v>0.98</v>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+      <c r="D201" s="23" t="n">
+        <v>971</v>
+      </c>
+      <c r="E201" s="24" t="n">
+        <v>1145720218</v>
+      </c>
+      <c r="F201" s="24" t="n">
+        <v>1179938</v>
+      </c>
+      <c r="G201" s="25">
+        <f>IFERROR(F201/F189-1,"")</f>
+        <v/>
+      </c>
+      <c r="H201" s="24" t="n">
+        <v>1041800</v>
+      </c>
+      <c r="I201" s="23" t="n">
+        <v>2389</v>
+      </c>
+      <c r="J201" s="23" t="n">
+        <v>4919</v>
+      </c>
+      <c r="K201" s="25" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="L201" s="26">
+        <f>J201/D201</f>
+        <v/>
+      </c>
+      <c r="M201" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="N201" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="O201" s="27" t="n">
+        <v>55</v>
+      </c>
+      <c r="P201" s="25" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -21276,7 +21388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P200"/>
+  <dimension ref="A1:P201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -31686,6 +31798,62 @@
         <v>0.97</v>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+      <c r="D201" s="23" t="n">
+        <v>1767</v>
+      </c>
+      <c r="E201" s="24" t="n">
+        <v>1731102454</v>
+      </c>
+      <c r="F201" s="24" t="n">
+        <v>979684</v>
+      </c>
+      <c r="G201" s="25">
+        <f>IFERROR(F201/F189-1,"")</f>
+        <v/>
+      </c>
+      <c r="H201" s="24" t="n">
+        <v>770000</v>
+      </c>
+      <c r="I201" s="23" t="n">
+        <v>4200</v>
+      </c>
+      <c r="J201" s="23" t="n">
+        <v>8727</v>
+      </c>
+      <c r="K201" s="25" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="L201" s="26">
+        <f>J201/D201</f>
+        <v/>
+      </c>
+      <c r="M201" s="26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N201" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="O201" s="27" t="n">
+        <v>46</v>
+      </c>
+      <c r="P201" s="25" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -31699,7 +31867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P200"/>
+  <dimension ref="A1:P201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -42109,6 +42277,62 @@
         <v>0.96</v>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+      <c r="D201" s="23" t="n">
+        <v>178</v>
+      </c>
+      <c r="E201" s="24" t="n">
+        <v>144340977</v>
+      </c>
+      <c r="F201" s="24" t="n">
+        <v>810904</v>
+      </c>
+      <c r="G201" s="25">
+        <f>IFERROR(F201/F189-1,"")</f>
+        <v/>
+      </c>
+      <c r="H201" s="24" t="n">
+        <v>780000</v>
+      </c>
+      <c r="I201" s="23" t="n">
+        <v>505</v>
+      </c>
+      <c r="J201" s="23" t="n">
+        <v>1107</v>
+      </c>
+      <c r="K201" s="25" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="L201" s="26">
+        <f>J201/D201</f>
+        <v/>
+      </c>
+      <c r="M201" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="N201" s="27" t="n">
+        <v>37</v>
+      </c>
+      <c r="O201" s="27" t="n">
+        <v>57</v>
+      </c>
+      <c r="P201" s="25" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -42122,7 +42346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P200"/>
+  <dimension ref="A1:P201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -52532,6 +52756,62 @@
         <v>0.97</v>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+      <c r="D201" s="23" t="n">
+        <v>940</v>
+      </c>
+      <c r="E201" s="24" t="n">
+        <v>853910550</v>
+      </c>
+      <c r="F201" s="24" t="n">
+        <v>908415</v>
+      </c>
+      <c r="G201" s="25">
+        <f>IFERROR(F201/F189-1,"")</f>
+        <v/>
+      </c>
+      <c r="H201" s="24" t="n">
+        <v>850000</v>
+      </c>
+      <c r="I201" s="23" t="n">
+        <v>2298</v>
+      </c>
+      <c r="J201" s="23" t="n">
+        <v>4706</v>
+      </c>
+      <c r="K201" s="25" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="L201" s="26">
+        <f>J201/D201</f>
+        <v/>
+      </c>
+      <c r="M201" s="26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N201" s="27" t="n">
+        <v>36</v>
+      </c>
+      <c r="O201" s="27" t="n">
+        <v>55</v>
+      </c>
+      <c r="P201" s="25" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -52545,7 +52825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P200"/>
+  <dimension ref="A1:P201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -62955,6 +63235,62 @@
         <v>0.96</v>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+      <c r="D201" s="23" t="n">
+        <v>571</v>
+      </c>
+      <c r="E201" s="24" t="n">
+        <v>634058871</v>
+      </c>
+      <c r="F201" s="24" t="n">
+        <v>1110436</v>
+      </c>
+      <c r="G201" s="25">
+        <f>IFERROR(F201/F189-1,"")</f>
+        <v/>
+      </c>
+      <c r="H201" s="24" t="n">
+        <v>957000</v>
+      </c>
+      <c r="I201" s="23" t="n">
+        <v>1201</v>
+      </c>
+      <c r="J201" s="23" t="n">
+        <v>2413</v>
+      </c>
+      <c r="K201" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L201" s="26">
+        <f>J201/D201</f>
+        <v/>
+      </c>
+      <c r="M201" s="26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N201" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="O201" s="27" t="n">
+        <v>57</v>
+      </c>
+      <c r="P201" s="25" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -62968,7 +63304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P200"/>
+  <dimension ref="A1:P201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -73378,6 +73714,62 @@
         <v>0.98</v>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+      <c r="D201" s="23" t="n">
+        <v>602</v>
+      </c>
+      <c r="E201" s="24" t="n">
+        <v>493380832</v>
+      </c>
+      <c r="F201" s="24" t="n">
+        <v>819569</v>
+      </c>
+      <c r="G201" s="25">
+        <f>IFERROR(F201/F189-1,"")</f>
+        <v/>
+      </c>
+      <c r="H201" s="24" t="n">
+        <v>766000</v>
+      </c>
+      <c r="I201" s="23" t="n">
+        <v>1423</v>
+      </c>
+      <c r="J201" s="23" t="n">
+        <v>2467</v>
+      </c>
+      <c r="K201" s="25" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="L201" s="26">
+        <f>J201/D201</f>
+        <v/>
+      </c>
+      <c r="M201" s="26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N201" s="27" t="n">
+        <v>31</v>
+      </c>
+      <c r="O201" s="27" t="n">
+        <v>46</v>
+      </c>
+      <c r="P201" s="25" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -73391,7 +73783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P200"/>
+  <dimension ref="A1:P201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -83801,6 +84193,62 @@
         <v>0.97</v>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+      <c r="D201" s="23" t="n">
+        <v>28</v>
+      </c>
+      <c r="E201" s="24" t="n">
+        <v>21161255</v>
+      </c>
+      <c r="F201" s="24" t="n">
+        <v>755759</v>
+      </c>
+      <c r="G201" s="25">
+        <f>IFERROR(F201/F189-1,"")</f>
+        <v/>
+      </c>
+      <c r="H201" s="24" t="n">
+        <v>755378</v>
+      </c>
+      <c r="I201" s="23" t="n">
+        <v>59</v>
+      </c>
+      <c r="J201" s="23" t="n">
+        <v>143</v>
+      </c>
+      <c r="K201" s="25" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L201" s="26">
+        <f>J201/D201</f>
+        <v/>
+      </c>
+      <c r="M201" s="26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N201" s="27" t="n">
+        <v>46</v>
+      </c>
+      <c r="O201" s="27" t="n">
+        <v>64</v>
+      </c>
+      <c r="P201" s="25" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
